--- a/data/1Saldos - ecossistema.xlsx
+++ b/data/1Saldos - ecossistema.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ALURA\Documents\Report de Saldos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{246AB44B-8902-48A1-B47A-F197C1E4F760}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{635DBF09-B66D-43F6-8D59-8EC20562D0F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7EA03BAB-5D16-49FA-97CC-A81D8C595687}"/>
+    <workbookView xWindow="28800" yWindow="720" windowWidth="29040" windowHeight="15480" xr2:uid="{7EA03BAB-5D16-49FA-97CC-A81D8C595687}"/>
   </bookViews>
   <sheets>
     <sheet name="in" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3960" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3986" uniqueCount="17">
   <si>
     <t>Empresa</t>
   </si>
@@ -958,7 +958,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31E222C4-9EE5-4085-8D2B-84513C2B1175}">
-  <dimension ref="A1:L1977"/>
+  <dimension ref="A1:L1990"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.5546875" bestFit="1" customWidth="1"/>
@@ -52374,6 +52374,344 @@
         <v>3069537.84</v>
       </c>
     </row>
+    <row r="1978" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1978" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1978" s="1">
+        <v>46076</v>
+      </c>
+      <c r="C1978" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1978">
+        <v>0</v>
+      </c>
+      <c r="E1978">
+        <v>0</v>
+      </c>
+      <c r="F1978">
+        <v>0</v>
+      </c>
+      <c r="G1978">
+        <v>998204.61</v>
+      </c>
+      <c r="H1978">
+        <v>998204.61</v>
+      </c>
+    </row>
+    <row r="1979" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1979" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1979" s="1">
+        <v>46076</v>
+      </c>
+      <c r="C1979" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1979">
+        <v>4950.1099999999997</v>
+      </c>
+      <c r="E1979">
+        <v>23316.41</v>
+      </c>
+      <c r="F1979">
+        <v>-18366.3</v>
+      </c>
+      <c r="G1979">
+        <v>6660241.46</v>
+      </c>
+      <c r="H1979">
+        <v>6641875.1600000001</v>
+      </c>
+    </row>
+    <row r="1980" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1980" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1980" s="1">
+        <v>46076</v>
+      </c>
+      <c r="C1980" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1980">
+        <v>342504.62</v>
+      </c>
+      <c r="E1980">
+        <v>0</v>
+      </c>
+      <c r="F1980">
+        <v>342504.62</v>
+      </c>
+      <c r="G1980">
+        <v>0</v>
+      </c>
+      <c r="H1980">
+        <v>342504.62</v>
+      </c>
+    </row>
+    <row r="1981" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1981" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1981" s="1">
+        <v>46076</v>
+      </c>
+      <c r="C1981" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1981">
+        <v>0</v>
+      </c>
+      <c r="E1981">
+        <v>0</v>
+      </c>
+      <c r="F1981">
+        <v>0</v>
+      </c>
+      <c r="G1981">
+        <v>14616606.970000001</v>
+      </c>
+      <c r="H1981">
+        <v>14616606.970000001</v>
+      </c>
+    </row>
+    <row r="1982" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1982" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1982" s="1">
+        <v>46076</v>
+      </c>
+      <c r="C1982" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1982">
+        <v>0</v>
+      </c>
+      <c r="E1982">
+        <v>0</v>
+      </c>
+      <c r="F1982">
+        <v>0</v>
+      </c>
+      <c r="G1982">
+        <v>243148.83</v>
+      </c>
+      <c r="H1982">
+        <v>243148.83</v>
+      </c>
+    </row>
+    <row r="1983" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1983" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1983" s="1">
+        <v>46076</v>
+      </c>
+      <c r="C1983" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1983">
+        <v>0</v>
+      </c>
+      <c r="E1983">
+        <v>0</v>
+      </c>
+      <c r="F1983">
+        <v>0</v>
+      </c>
+      <c r="G1983">
+        <v>2805161.33</v>
+      </c>
+      <c r="H1983">
+        <v>2805161.33</v>
+      </c>
+    </row>
+    <row r="1984" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1984" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1984" s="1">
+        <v>46076</v>
+      </c>
+      <c r="C1984" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1984">
+        <v>296720.28999999998</v>
+      </c>
+      <c r="E1984">
+        <v>87908.22</v>
+      </c>
+      <c r="F1984">
+        <v>208812.06999999998</v>
+      </c>
+      <c r="G1984">
+        <v>9056024.4399999995</v>
+      </c>
+      <c r="H1984">
+        <v>9264836.5099999998</v>
+      </c>
+    </row>
+    <row r="1985" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1985" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1985" s="1">
+        <v>46076</v>
+      </c>
+      <c r="C1985" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1985">
+        <v>0</v>
+      </c>
+      <c r="E1985">
+        <v>0</v>
+      </c>
+      <c r="F1985">
+        <v>0</v>
+      </c>
+      <c r="G1985">
+        <v>72327.7</v>
+      </c>
+      <c r="H1985">
+        <v>72327.7</v>
+      </c>
+    </row>
+    <row r="1986" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1986" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1986" s="1">
+        <v>46076</v>
+      </c>
+      <c r="C1986" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1986">
+        <v>0</v>
+      </c>
+      <c r="E1986">
+        <v>0</v>
+      </c>
+      <c r="F1986">
+        <v>0</v>
+      </c>
+      <c r="G1986">
+        <v>51688803.670000002</v>
+      </c>
+      <c r="H1986">
+        <v>51688803.670000002</v>
+      </c>
+    </row>
+    <row r="1987" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1987" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1987" s="1">
+        <v>46076</v>
+      </c>
+      <c r="C1987" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1987">
+        <v>0</v>
+      </c>
+      <c r="E1987">
+        <v>0</v>
+      </c>
+      <c r="F1987">
+        <v>0</v>
+      </c>
+      <c r="G1987">
+        <v>374340.82</v>
+      </c>
+      <c r="H1987">
+        <v>374340.82</v>
+      </c>
+    </row>
+    <row r="1988" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1988" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1988" s="1">
+        <v>46076</v>
+      </c>
+      <c r="C1988" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1988">
+        <v>0</v>
+      </c>
+      <c r="E1988">
+        <v>0</v>
+      </c>
+      <c r="F1988">
+        <v>0</v>
+      </c>
+      <c r="G1988">
+        <v>1066975.28</v>
+      </c>
+      <c r="H1988">
+        <v>1066975.28</v>
+      </c>
+    </row>
+    <row r="1989" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1989" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1989" s="1">
+        <v>46076</v>
+      </c>
+      <c r="C1989" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1989">
+        <v>5000.4399999999996</v>
+      </c>
+      <c r="E1989">
+        <v>0</v>
+      </c>
+      <c r="F1989">
+        <v>5000.4399999999996</v>
+      </c>
+      <c r="G1989">
+        <v>16544.12</v>
+      </c>
+      <c r="H1989">
+        <v>21544.559999999998</v>
+      </c>
+    </row>
+    <row r="1990" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1990" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1990" s="1">
+        <v>46076</v>
+      </c>
+      <c r="C1990" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1990">
+        <v>0</v>
+      </c>
+      <c r="E1990">
+        <v>0</v>
+      </c>
+      <c r="F1990">
+        <v>0</v>
+      </c>
+      <c r="G1990">
+        <v>3071236.72</v>
+      </c>
+      <c r="H1990">
+        <v>3071236.72</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:L1691" xr:uid="{31E222C4-9EE5-4085-8D2B-84513C2B1175}"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>

--- a/data/1Saldos - ecossistema.xlsx
+++ b/data/1Saldos - ecossistema.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ALURA\Documents\Report de Saldos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{635DBF09-B66D-43F6-8D59-8EC20562D0F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5697AE55-5280-48F7-B681-7537C9AFC72B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28800" yWindow="720" windowWidth="29040" windowHeight="15480" xr2:uid="{7EA03BAB-5D16-49FA-97CC-A81D8C595687}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7EA03BAB-5D16-49FA-97CC-A81D8C595687}"/>
   </bookViews>
   <sheets>
     <sheet name="in" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3986" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4012" uniqueCount="17">
   <si>
     <t>Empresa</t>
   </si>
@@ -958,7 +958,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31E222C4-9EE5-4085-8D2B-84513C2B1175}">
-  <dimension ref="A1:L1990"/>
+  <dimension ref="A1:L2003"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.5546875" bestFit="1" customWidth="1"/>
@@ -52712,6 +52712,344 @@
         <v>3071236.72</v>
       </c>
     </row>
+    <row r="1991" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1991" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1991" s="1">
+        <v>46077</v>
+      </c>
+      <c r="C1991" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1991">
+        <v>0</v>
+      </c>
+      <c r="E1991">
+        <v>0</v>
+      </c>
+      <c r="F1991">
+        <v>0</v>
+      </c>
+      <c r="G1991">
+        <v>998204.61</v>
+      </c>
+      <c r="H1991">
+        <v>998204.61</v>
+      </c>
+    </row>
+    <row r="1992" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1992" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1992" s="1">
+        <v>46077</v>
+      </c>
+      <c r="C1992" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1992">
+        <v>29587.07</v>
+      </c>
+      <c r="E1992">
+        <v>0</v>
+      </c>
+      <c r="F1992">
+        <v>29587.07</v>
+      </c>
+      <c r="G1992">
+        <v>6881841.0300000003</v>
+      </c>
+      <c r="H1992">
+        <v>6911428.1000000006</v>
+      </c>
+    </row>
+    <row r="1993" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1993" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1993" s="1">
+        <v>46077</v>
+      </c>
+      <c r="C1993" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1993">
+        <v>651846.63</v>
+      </c>
+      <c r="E1993">
+        <v>0</v>
+      </c>
+      <c r="F1993">
+        <v>651846.63</v>
+      </c>
+      <c r="G1993">
+        <v>0</v>
+      </c>
+      <c r="H1993">
+        <v>651846.63</v>
+      </c>
+    </row>
+    <row r="1994" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1994" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1994" s="1">
+        <v>46077</v>
+      </c>
+      <c r="C1994" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1994">
+        <v>0</v>
+      </c>
+      <c r="E1994">
+        <v>0</v>
+      </c>
+      <c r="F1994">
+        <v>0</v>
+      </c>
+      <c r="G1994">
+        <v>14619717.800000001</v>
+      </c>
+      <c r="H1994">
+        <v>14619717.800000001</v>
+      </c>
+    </row>
+    <row r="1995" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1995" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1995" s="1">
+        <v>46077</v>
+      </c>
+      <c r="C1995" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1995">
+        <v>0</v>
+      </c>
+      <c r="E1995">
+        <v>0</v>
+      </c>
+      <c r="F1995">
+        <v>0</v>
+      </c>
+      <c r="G1995">
+        <v>516719.44</v>
+      </c>
+      <c r="H1995">
+        <v>516719.44</v>
+      </c>
+    </row>
+    <row r="1996" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1996" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1996" s="1">
+        <v>46077</v>
+      </c>
+      <c r="C1996" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1996">
+        <v>0</v>
+      </c>
+      <c r="E1996">
+        <v>0</v>
+      </c>
+      <c r="F1996">
+        <v>0</v>
+      </c>
+      <c r="G1996">
+        <v>2805161.33</v>
+      </c>
+      <c r="H1996">
+        <v>2805161.33</v>
+      </c>
+    </row>
+    <row r="1997" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1997" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1997" s="1">
+        <v>46077</v>
+      </c>
+      <c r="C1997" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1997">
+        <v>18242.98</v>
+      </c>
+      <c r="E1997">
+        <v>0</v>
+      </c>
+      <c r="F1997">
+        <v>18242.98</v>
+      </c>
+      <c r="G1997">
+        <v>11088281.390000001</v>
+      </c>
+      <c r="H1997">
+        <v>11106524.370000001</v>
+      </c>
+    </row>
+    <row r="1998" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1998" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1998" s="1">
+        <v>46077</v>
+      </c>
+      <c r="C1998" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1998">
+        <v>0</v>
+      </c>
+      <c r="E1998">
+        <v>443.46</v>
+      </c>
+      <c r="F1998">
+        <v>-443.46</v>
+      </c>
+      <c r="G1998">
+        <v>72327.7</v>
+      </c>
+      <c r="H1998">
+        <v>71884.239999999991</v>
+      </c>
+    </row>
+    <row r="1999" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1999" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1999" s="1">
+        <v>46077</v>
+      </c>
+      <c r="C1999" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1999">
+        <v>0</v>
+      </c>
+      <c r="E1999">
+        <v>0</v>
+      </c>
+      <c r="F1999">
+        <v>0</v>
+      </c>
+      <c r="G1999">
+        <v>3071941.31</v>
+      </c>
+      <c r="H1999">
+        <v>3071941.31</v>
+      </c>
+    </row>
+    <row r="2000" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2000" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2000" s="1">
+        <v>46077</v>
+      </c>
+      <c r="C2000" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2000">
+        <v>0</v>
+      </c>
+      <c r="E2000">
+        <v>0</v>
+      </c>
+      <c r="F2000">
+        <v>0</v>
+      </c>
+      <c r="G2000">
+        <v>374340.82</v>
+      </c>
+      <c r="H2000">
+        <v>374340.82</v>
+      </c>
+    </row>
+    <row r="2001" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2001" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2001" s="1">
+        <v>46077</v>
+      </c>
+      <c r="C2001" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2001">
+        <v>0</v>
+      </c>
+      <c r="E2001">
+        <v>0</v>
+      </c>
+      <c r="F2001">
+        <v>0</v>
+      </c>
+      <c r="G2001">
+        <v>1067420.67</v>
+      </c>
+      <c r="H2001">
+        <v>1067420.67</v>
+      </c>
+    </row>
+    <row r="2002" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2002" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B2002" s="1">
+        <v>46077</v>
+      </c>
+      <c r="C2002" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2002">
+        <v>10009</v>
+      </c>
+      <c r="E2002">
+        <v>0</v>
+      </c>
+      <c r="F2002">
+        <v>10009</v>
+      </c>
+      <c r="G2002">
+        <v>75475.539999999994</v>
+      </c>
+      <c r="H2002">
+        <v>85484.54</v>
+      </c>
+    </row>
+    <row r="2003" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2003" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B2003" s="1">
+        <v>46077</v>
+      </c>
+      <c r="C2003" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2003">
+        <v>0</v>
+      </c>
+      <c r="E2003">
+        <v>0</v>
+      </c>
+      <c r="F2003">
+        <v>0</v>
+      </c>
+      <c r="G2003">
+        <v>51707703.960000001</v>
+      </c>
+      <c r="H2003">
+        <v>51707703.960000001</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:L1691" xr:uid="{31E222C4-9EE5-4085-8D2B-84513C2B1175}"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>

--- a/data/1Saldos - ecossistema.xlsx
+++ b/data/1Saldos - ecossistema.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ALURA\Documents\Report de Saldos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5697AE55-5280-48F7-B681-7537C9AFC72B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05308BED-1DAF-4885-89AF-D0AEB6A1CC6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7EA03BAB-5D16-49FA-97CC-A81D8C595687}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4012" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4038" uniqueCount="17">
   <si>
     <t>Empresa</t>
   </si>
@@ -958,7 +958,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31E222C4-9EE5-4085-8D2B-84513C2B1175}">
-  <dimension ref="A1:L2003"/>
+  <dimension ref="A1:L2016"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.5546875" bestFit="1" customWidth="1"/>
@@ -53050,6 +53050,344 @@
         <v>51707703.960000001</v>
       </c>
     </row>
+    <row r="2004" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2004" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2004" s="1">
+        <v>46078</v>
+      </c>
+      <c r="C2004" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2004">
+        <v>0</v>
+      </c>
+      <c r="E2004">
+        <v>0</v>
+      </c>
+      <c r="F2004">
+        <v>0</v>
+      </c>
+      <c r="G2004">
+        <v>998204.61</v>
+      </c>
+      <c r="H2004">
+        <v>998204.61</v>
+      </c>
+    </row>
+    <row r="2005" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2005" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2005" s="1">
+        <v>46078</v>
+      </c>
+      <c r="C2005" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2005">
+        <v>10014.299999999999</v>
+      </c>
+      <c r="E2005">
+        <v>1108934.46</v>
+      </c>
+      <c r="F2005">
+        <v>-1098920.1599999999</v>
+      </c>
+      <c r="G2005">
+        <v>8123914.7000000002</v>
+      </c>
+      <c r="H2005">
+        <v>7024994.54</v>
+      </c>
+    </row>
+    <row r="2006" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2006" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2006" s="1">
+        <v>46078</v>
+      </c>
+      <c r="C2006" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2006">
+        <v>291149.34000000003</v>
+      </c>
+      <c r="E2006">
+        <v>0</v>
+      </c>
+      <c r="F2006">
+        <v>291149.34000000003</v>
+      </c>
+      <c r="G2006">
+        <v>0</v>
+      </c>
+      <c r="H2006">
+        <v>291149.34000000003</v>
+      </c>
+    </row>
+    <row r="2007" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2007" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2007" s="1">
+        <v>46078</v>
+      </c>
+      <c r="C2007" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2007">
+        <v>0</v>
+      </c>
+      <c r="E2007">
+        <v>0</v>
+      </c>
+      <c r="F2007">
+        <v>0</v>
+      </c>
+      <c r="G2007">
+        <v>14619717.800000001</v>
+      </c>
+      <c r="H2007">
+        <v>14619717.800000001</v>
+      </c>
+    </row>
+    <row r="2008" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2008" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2008" s="1">
+        <v>46078</v>
+      </c>
+      <c r="C2008" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2008">
+        <v>0</v>
+      </c>
+      <c r="E2008">
+        <v>0</v>
+      </c>
+      <c r="F2008">
+        <v>0</v>
+      </c>
+      <c r="G2008">
+        <v>500940.04</v>
+      </c>
+      <c r="H2008">
+        <v>500940.04</v>
+      </c>
+    </row>
+    <row r="2009" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2009" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2009" s="1">
+        <v>46078</v>
+      </c>
+      <c r="C2009" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2009">
+        <v>0</v>
+      </c>
+      <c r="E2009">
+        <v>0</v>
+      </c>
+      <c r="F2009">
+        <v>0</v>
+      </c>
+      <c r="G2009">
+        <v>2805161.33</v>
+      </c>
+      <c r="H2009">
+        <v>2805161.33</v>
+      </c>
+    </row>
+    <row r="2010" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2010" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2010" s="1">
+        <v>46078</v>
+      </c>
+      <c r="C2010" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2010">
+        <v>75998.899999999994</v>
+      </c>
+      <c r="E2010">
+        <v>1427757.62</v>
+      </c>
+      <c r="F2010">
+        <v>-1351758.7200000002</v>
+      </c>
+      <c r="G2010">
+        <v>11653479.43</v>
+      </c>
+      <c r="H2010">
+        <v>10301720.709999999</v>
+      </c>
+    </row>
+    <row r="2011" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2011" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2011" s="1">
+        <v>46078</v>
+      </c>
+      <c r="C2011" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2011">
+        <v>0</v>
+      </c>
+      <c r="E2011">
+        <v>0</v>
+      </c>
+      <c r="F2011">
+        <v>0</v>
+      </c>
+      <c r="G2011">
+        <v>71884.240000000005</v>
+      </c>
+      <c r="H2011">
+        <v>71884.240000000005</v>
+      </c>
+    </row>
+    <row r="2012" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2012" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2012" s="1">
+        <v>46078</v>
+      </c>
+      <c r="C2012" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2012">
+        <v>0</v>
+      </c>
+      <c r="E2012">
+        <v>0</v>
+      </c>
+      <c r="F2012">
+        <v>0</v>
+      </c>
+      <c r="G2012">
+        <v>51710097.609999999</v>
+      </c>
+      <c r="H2012">
+        <v>51710097.609999999</v>
+      </c>
+    </row>
+    <row r="2013" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2013" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2013" s="1">
+        <v>46078</v>
+      </c>
+      <c r="C2013" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2013">
+        <v>0</v>
+      </c>
+      <c r="E2013">
+        <v>0</v>
+      </c>
+      <c r="F2013">
+        <v>0</v>
+      </c>
+      <c r="G2013">
+        <v>374340.82</v>
+      </c>
+      <c r="H2013">
+        <v>374340.82</v>
+      </c>
+    </row>
+    <row r="2014" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2014" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2014" s="1">
+        <v>46078</v>
+      </c>
+      <c r="C2014" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2014">
+        <v>0</v>
+      </c>
+      <c r="E2014">
+        <v>0</v>
+      </c>
+      <c r="F2014">
+        <v>0</v>
+      </c>
+      <c r="G2014">
+        <v>1067689.27</v>
+      </c>
+      <c r="H2014">
+        <v>1067689.27</v>
+      </c>
+    </row>
+    <row r="2015" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2015" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B2015" s="1">
+        <v>46078</v>
+      </c>
+      <c r="C2015" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2015">
+        <v>5007.96</v>
+      </c>
+      <c r="E2015">
+        <v>66532.009999999995</v>
+      </c>
+      <c r="F2015">
+        <v>-61524.049999999996</v>
+      </c>
+      <c r="G2015">
+        <v>123283.33</v>
+      </c>
+      <c r="H2015">
+        <v>61759.280000000006</v>
+      </c>
+    </row>
+    <row r="2016" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2016" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B2016" s="1">
+        <v>46078</v>
+      </c>
+      <c r="C2016" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2016">
+        <v>0</v>
+      </c>
+      <c r="E2016">
+        <v>0</v>
+      </c>
+      <c r="F2016">
+        <v>0</v>
+      </c>
+      <c r="G2016">
+        <v>3072817.68</v>
+      </c>
+      <c r="H2016">
+        <v>3072817.68</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:L1691" xr:uid="{31E222C4-9EE5-4085-8D2B-84513C2B1175}"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>

--- a/data/1Saldos - ecossistema.xlsx
+++ b/data/1Saldos - ecossistema.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ALURA\Documents\Report de Saldos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05308BED-1DAF-4885-89AF-D0AEB6A1CC6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3BD765C-E99A-4FBC-825A-929826C4BDD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7EA03BAB-5D16-49FA-97CC-A81D8C595687}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4038" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4064" uniqueCount="17">
   <si>
     <t>Empresa</t>
   </si>
@@ -958,7 +958,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31E222C4-9EE5-4085-8D2B-84513C2B1175}">
-  <dimension ref="A1:L2016"/>
+  <dimension ref="A1:L2029"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.5546875" bestFit="1" customWidth="1"/>
@@ -53388,6 +53388,344 @@
         <v>3072817.68</v>
       </c>
     </row>
+    <row r="2017" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2017" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2017" s="1">
+        <v>46079</v>
+      </c>
+      <c r="C2017" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2017">
+        <v>0</v>
+      </c>
+      <c r="E2017">
+        <v>0</v>
+      </c>
+      <c r="F2017">
+        <v>0</v>
+      </c>
+      <c r="G2017">
+        <v>998204.61</v>
+      </c>
+      <c r="H2017">
+        <v>998204.61</v>
+      </c>
+    </row>
+    <row r="2018" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2018" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2018" s="1">
+        <v>46079</v>
+      </c>
+      <c r="C2018" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2018">
+        <v>12136.86</v>
+      </c>
+      <c r="E2018">
+        <v>0</v>
+      </c>
+      <c r="F2018">
+        <v>12136.86</v>
+      </c>
+      <c r="G2018">
+        <v>8119720.3899999997</v>
+      </c>
+      <c r="H2018">
+        <v>8131857.25</v>
+      </c>
+    </row>
+    <row r="2019" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2019" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2019" s="1">
+        <v>46079</v>
+      </c>
+      <c r="C2019" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2019">
+        <v>211332.12</v>
+      </c>
+      <c r="E2019">
+        <v>0</v>
+      </c>
+      <c r="F2019">
+        <v>211332.12</v>
+      </c>
+      <c r="G2019">
+        <v>0</v>
+      </c>
+      <c r="H2019">
+        <v>211332.12</v>
+      </c>
+    </row>
+    <row r="2020" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2020" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2020" s="1">
+        <v>46079</v>
+      </c>
+      <c r="C2020" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2020">
+        <v>0</v>
+      </c>
+      <c r="E2020">
+        <v>0</v>
+      </c>
+      <c r="F2020">
+        <v>0</v>
+      </c>
+      <c r="G2020">
+        <v>14614593.859999999</v>
+      </c>
+      <c r="H2020">
+        <v>14614593.859999999</v>
+      </c>
+    </row>
+    <row r="2021" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2021" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2021" s="1">
+        <v>46079</v>
+      </c>
+      <c r="C2021" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2021">
+        <v>0</v>
+      </c>
+      <c r="E2021">
+        <v>0</v>
+      </c>
+      <c r="F2021">
+        <v>0</v>
+      </c>
+      <c r="G2021">
+        <v>122258.46</v>
+      </c>
+      <c r="H2021">
+        <v>122258.46</v>
+      </c>
+    </row>
+    <row r="2022" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2022" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2022" s="1">
+        <v>46079</v>
+      </c>
+      <c r="C2022" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2022">
+        <v>0</v>
+      </c>
+      <c r="E2022">
+        <v>0</v>
+      </c>
+      <c r="F2022">
+        <v>0</v>
+      </c>
+      <c r="G2022">
+        <v>2805161.33</v>
+      </c>
+      <c r="H2022">
+        <v>2805161.33</v>
+      </c>
+    </row>
+    <row r="2023" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2023" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2023" s="1">
+        <v>46079</v>
+      </c>
+      <c r="C2023" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2023">
+        <v>133807.46</v>
+      </c>
+      <c r="E2023">
+        <v>0</v>
+      </c>
+      <c r="F2023">
+        <v>133807.46</v>
+      </c>
+      <c r="G2023">
+        <v>10483193</v>
+      </c>
+      <c r="H2023">
+        <v>10617000.460000001</v>
+      </c>
+    </row>
+    <row r="2024" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2024" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2024" s="1">
+        <v>46079</v>
+      </c>
+      <c r="C2024" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2024">
+        <v>0</v>
+      </c>
+      <c r="E2024">
+        <v>0</v>
+      </c>
+      <c r="F2024">
+        <v>0</v>
+      </c>
+      <c r="G2024">
+        <v>71884.240000000005</v>
+      </c>
+      <c r="H2024">
+        <v>71884.240000000005</v>
+      </c>
+    </row>
+    <row r="2025" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2025" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2025" s="1">
+        <v>46079</v>
+      </c>
+      <c r="C2025" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2025">
+        <v>0</v>
+      </c>
+      <c r="E2025">
+        <v>0</v>
+      </c>
+      <c r="F2025">
+        <v>0</v>
+      </c>
+      <c r="G2025">
+        <v>51769520.770000003</v>
+      </c>
+      <c r="H2025">
+        <v>51769520.770000003</v>
+      </c>
+    </row>
+    <row r="2026" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2026" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2026" s="1">
+        <v>46079</v>
+      </c>
+      <c r="C2026" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2026">
+        <v>0</v>
+      </c>
+      <c r="E2026">
+        <v>100000</v>
+      </c>
+      <c r="F2026">
+        <v>-100000</v>
+      </c>
+      <c r="G2026">
+        <v>374340.82</v>
+      </c>
+      <c r="H2026">
+        <v>274340.82</v>
+      </c>
+    </row>
+    <row r="2027" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2027" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2027" s="1">
+        <v>46079</v>
+      </c>
+      <c r="C2027" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2027">
+        <v>0</v>
+      </c>
+      <c r="E2027">
+        <v>0</v>
+      </c>
+      <c r="F2027">
+        <v>0</v>
+      </c>
+      <c r="G2027">
+        <v>1068257.8999999999</v>
+      </c>
+      <c r="H2027">
+        <v>1068257.8999999999</v>
+      </c>
+    </row>
+    <row r="2028" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2028" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B2028" s="1">
+        <v>46079</v>
+      </c>
+      <c r="C2028" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2028">
+        <v>4025.65</v>
+      </c>
+      <c r="E2028">
+        <v>0</v>
+      </c>
+      <c r="F2028">
+        <v>4025.65</v>
+      </c>
+      <c r="G2028">
+        <v>273327.59000000003</v>
+      </c>
+      <c r="H2028">
+        <v>277353.24000000005</v>
+      </c>
+    </row>
+    <row r="2029" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2029" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B2029" s="1">
+        <v>46079</v>
+      </c>
+      <c r="C2029" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2029">
+        <v>0</v>
+      </c>
+      <c r="E2029">
+        <v>0</v>
+      </c>
+      <c r="F2029">
+        <v>0</v>
+      </c>
+      <c r="G2029">
+        <v>3074623.06</v>
+      </c>
+      <c r="H2029">
+        <v>3074623.06</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:L1691" xr:uid="{31E222C4-9EE5-4085-8D2B-84513C2B1175}"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>

--- a/data/1Saldos - ecossistema.xlsx
+++ b/data/1Saldos - ecossistema.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ALURA\Documents\Report de Saldos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3BD765C-E99A-4FBC-825A-929826C4BDD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{809D9415-0EAB-4696-8886-CA0C9194814D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7EA03BAB-5D16-49FA-97CC-A81D8C595687}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4064" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4090" uniqueCount="17">
   <si>
     <t>Empresa</t>
   </si>
@@ -958,7 +958,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31E222C4-9EE5-4085-8D2B-84513C2B1175}">
-  <dimension ref="A1:L2029"/>
+  <dimension ref="A1:L2042"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.5546875" bestFit="1" customWidth="1"/>
@@ -53726,6 +53726,344 @@
         <v>3074623.06</v>
       </c>
     </row>
+    <row r="2030" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2030" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2030" s="1">
+        <v>46080</v>
+      </c>
+      <c r="C2030" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2030">
+        <v>0</v>
+      </c>
+      <c r="E2030">
+        <v>0</v>
+      </c>
+      <c r="F2030">
+        <v>0</v>
+      </c>
+      <c r="G2030">
+        <v>998204.61</v>
+      </c>
+      <c r="H2030">
+        <v>998204.61</v>
+      </c>
+    </row>
+    <row r="2031" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2031" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2031" s="1">
+        <v>46080</v>
+      </c>
+      <c r="C2031" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2031">
+        <v>10032.09</v>
+      </c>
+      <c r="E2031">
+        <v>64562.080000000002</v>
+      </c>
+      <c r="F2031">
+        <v>-54529.990000000005</v>
+      </c>
+      <c r="G2031">
+        <v>8232967.0800000001</v>
+      </c>
+      <c r="H2031">
+        <v>8178437.0899999999</v>
+      </c>
+    </row>
+    <row r="2032" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2032" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2032" s="1">
+        <v>46080</v>
+      </c>
+      <c r="C2032" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2032">
+        <v>324547.65999999997</v>
+      </c>
+      <c r="E2032">
+        <v>0</v>
+      </c>
+      <c r="F2032">
+        <v>324547.65999999997</v>
+      </c>
+      <c r="G2032">
+        <v>0</v>
+      </c>
+      <c r="H2032">
+        <v>324547.65999999997</v>
+      </c>
+    </row>
+    <row r="2033" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2033" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2033" s="1">
+        <v>46080</v>
+      </c>
+      <c r="C2033" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2033">
+        <v>0</v>
+      </c>
+      <c r="E2033">
+        <v>0</v>
+      </c>
+      <c r="F2033">
+        <v>0</v>
+      </c>
+      <c r="G2033">
+        <v>14624586.35</v>
+      </c>
+      <c r="H2033">
+        <v>14624586.35</v>
+      </c>
+    </row>
+    <row r="2034" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2034" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2034" s="1">
+        <v>46080</v>
+      </c>
+      <c r="C2034" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2034">
+        <v>0</v>
+      </c>
+      <c r="E2034">
+        <v>0</v>
+      </c>
+      <c r="F2034">
+        <v>0</v>
+      </c>
+      <c r="G2034">
+        <v>351841.34</v>
+      </c>
+      <c r="H2034">
+        <v>351841.34</v>
+      </c>
+    </row>
+    <row r="2035" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2035" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2035" s="1">
+        <v>46080</v>
+      </c>
+      <c r="C2035" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2035">
+        <v>0</v>
+      </c>
+      <c r="E2035">
+        <v>0</v>
+      </c>
+      <c r="F2035">
+        <v>0</v>
+      </c>
+      <c r="G2035">
+        <v>2805161.33</v>
+      </c>
+      <c r="H2035">
+        <v>2805161.33</v>
+      </c>
+    </row>
+    <row r="2036" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2036" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2036" s="1">
+        <v>46080</v>
+      </c>
+      <c r="C2036" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2036">
+        <v>58923.03</v>
+      </c>
+      <c r="E2036">
+        <v>17921.79</v>
+      </c>
+      <c r="F2036">
+        <v>41001.24</v>
+      </c>
+      <c r="G2036">
+        <v>11338100.060000001</v>
+      </c>
+      <c r="H2036">
+        <v>11379101.300000001</v>
+      </c>
+    </row>
+    <row r="2037" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2037" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2037" s="1">
+        <v>46080</v>
+      </c>
+      <c r="C2037" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2037">
+        <v>0</v>
+      </c>
+      <c r="E2037">
+        <v>36131.01</v>
+      </c>
+      <c r="F2037">
+        <v>-36131.01</v>
+      </c>
+      <c r="G2037">
+        <v>71884.240000000005</v>
+      </c>
+      <c r="H2037">
+        <v>35753.230000000003</v>
+      </c>
+    </row>
+    <row r="2038" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2038" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2038" s="1">
+        <v>46080</v>
+      </c>
+      <c r="C2038" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2038">
+        <v>0</v>
+      </c>
+      <c r="E2038">
+        <v>0</v>
+      </c>
+      <c r="F2038">
+        <v>0</v>
+      </c>
+      <c r="G2038">
+        <v>51798682.920000002</v>
+      </c>
+      <c r="H2038">
+        <v>51798682.920000002</v>
+      </c>
+    </row>
+    <row r="2039" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2039" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2039" s="1">
+        <v>46080</v>
+      </c>
+      <c r="C2039" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2039">
+        <v>0</v>
+      </c>
+      <c r="E2039">
+        <v>0</v>
+      </c>
+      <c r="F2039">
+        <v>0</v>
+      </c>
+      <c r="G2039">
+        <v>374340.82</v>
+      </c>
+      <c r="H2039">
+        <v>374340.82</v>
+      </c>
+    </row>
+    <row r="2040" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2040" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2040" s="1">
+        <v>46080</v>
+      </c>
+      <c r="C2040" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2040">
+        <v>0</v>
+      </c>
+      <c r="E2040">
+        <v>0</v>
+      </c>
+      <c r="F2040">
+        <v>0</v>
+      </c>
+      <c r="G2040">
+        <v>1069227.06</v>
+      </c>
+      <c r="H2040">
+        <v>1069227.06</v>
+      </c>
+    </row>
+    <row r="2041" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2041" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B2041" s="1">
+        <v>46080</v>
+      </c>
+      <c r="C2041" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2041">
+        <v>5016.4799999999996</v>
+      </c>
+      <c r="E2041">
+        <v>0</v>
+      </c>
+      <c r="F2041">
+        <v>5016.4799999999996</v>
+      </c>
+      <c r="G2041">
+        <v>303464.53000000003</v>
+      </c>
+      <c r="H2041">
+        <v>308481.01</v>
+      </c>
+    </row>
+    <row r="2042" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2042" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B2042" s="1">
+        <v>46080</v>
+      </c>
+      <c r="C2042" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2042">
+        <v>0</v>
+      </c>
+      <c r="E2042">
+        <v>0</v>
+      </c>
+      <c r="F2042">
+        <v>0</v>
+      </c>
+      <c r="G2042">
+        <v>3078747.59</v>
+      </c>
+      <c r="H2042">
+        <v>3078747.59</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:L1691" xr:uid="{31E222C4-9EE5-4085-8D2B-84513C2B1175}"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>

--- a/data/1Saldos - ecossistema.xlsx
+++ b/data/1Saldos - ecossistema.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ALURA\Documents\Report de Saldos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{809D9415-0EAB-4696-8886-CA0C9194814D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F2FFAFC-2E6B-460F-88FC-3E2218DAB8E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7EA03BAB-5D16-49FA-97CC-A81D8C595687}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4090" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4116" uniqueCount="17">
   <si>
     <t>Empresa</t>
   </si>
@@ -958,7 +958,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31E222C4-9EE5-4085-8D2B-84513C2B1175}">
-  <dimension ref="A1:L2042"/>
+  <dimension ref="A1:L2055"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.5546875" bestFit="1" customWidth="1"/>
@@ -54064,6 +54064,344 @@
         <v>3078747.59</v>
       </c>
     </row>
+    <row r="2043" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2043" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2043" s="1">
+        <v>46083</v>
+      </c>
+      <c r="C2043" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2043">
+        <v>0</v>
+      </c>
+      <c r="E2043">
+        <v>0</v>
+      </c>
+      <c r="F2043">
+        <v>0</v>
+      </c>
+      <c r="G2043">
+        <v>998204.61</v>
+      </c>
+      <c r="H2043">
+        <v>998204.61</v>
+      </c>
+    </row>
+    <row r="2044" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2044" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2044" s="1">
+        <v>46083</v>
+      </c>
+      <c r="C2044" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2044">
+        <v>361808.4</v>
+      </c>
+      <c r="E2044">
+        <v>3470048.09</v>
+      </c>
+      <c r="F2044">
+        <v>-3108239.69</v>
+      </c>
+      <c r="G2044">
+        <v>8323676.5899999999</v>
+      </c>
+      <c r="H2044">
+        <v>5215436.9000000004</v>
+      </c>
+    </row>
+    <row r="2045" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2045" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2045" s="1">
+        <v>46083</v>
+      </c>
+      <c r="C2045" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2045">
+        <v>390126.31</v>
+      </c>
+      <c r="E2045">
+        <v>0</v>
+      </c>
+      <c r="F2045">
+        <v>390126.31</v>
+      </c>
+      <c r="G2045">
+        <v>0</v>
+      </c>
+      <c r="H2045">
+        <v>390126.31</v>
+      </c>
+    </row>
+    <row r="2046" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2046" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2046" s="1">
+        <v>46083</v>
+      </c>
+      <c r="C2046" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2046">
+        <v>0</v>
+      </c>
+      <c r="E2046">
+        <v>0</v>
+      </c>
+      <c r="F2046">
+        <v>0</v>
+      </c>
+      <c r="G2046">
+        <v>14634941.17</v>
+      </c>
+      <c r="H2046">
+        <v>14634941.17</v>
+      </c>
+    </row>
+    <row r="2047" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2047" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2047" s="1">
+        <v>46083</v>
+      </c>
+      <c r="C2047" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2047">
+        <v>0</v>
+      </c>
+      <c r="E2047">
+        <v>0</v>
+      </c>
+      <c r="F2047">
+        <v>0</v>
+      </c>
+      <c r="G2047">
+        <v>464081.98</v>
+      </c>
+      <c r="H2047">
+        <v>464081.98</v>
+      </c>
+    </row>
+    <row r="2048" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2048" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2048" s="1">
+        <v>46083</v>
+      </c>
+      <c r="C2048" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2048">
+        <v>0</v>
+      </c>
+      <c r="E2048">
+        <v>0</v>
+      </c>
+      <c r="F2048">
+        <v>0</v>
+      </c>
+      <c r="G2048">
+        <v>2805161.33</v>
+      </c>
+      <c r="H2048">
+        <v>2805161.33</v>
+      </c>
+    </row>
+    <row r="2049" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2049" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2049" s="1">
+        <v>46083</v>
+      </c>
+      <c r="C2049" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2049">
+        <v>127666.57</v>
+      </c>
+      <c r="E2049">
+        <v>45981.81</v>
+      </c>
+      <c r="F2049">
+        <v>81684.760000000009</v>
+      </c>
+      <c r="G2049">
+        <v>6178172</v>
+      </c>
+      <c r="H2049">
+        <v>6259856.7599999998</v>
+      </c>
+    </row>
+    <row r="2050" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2050" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2050" s="1">
+        <v>46083</v>
+      </c>
+      <c r="C2050" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2050">
+        <v>0</v>
+      </c>
+      <c r="E2050">
+        <v>6115688.5899999999</v>
+      </c>
+      <c r="F2050">
+        <v>-6115688.5899999999</v>
+      </c>
+      <c r="G2050">
+        <v>6237514.3499999996</v>
+      </c>
+      <c r="H2050">
+        <v>121825.75999999978</v>
+      </c>
+    </row>
+    <row r="2051" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2051" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2051" s="1">
+        <v>46083</v>
+      </c>
+      <c r="C2051" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2051">
+        <v>0</v>
+      </c>
+      <c r="E2051">
+        <v>0</v>
+      </c>
+      <c r="F2051">
+        <v>0</v>
+      </c>
+      <c r="G2051">
+        <v>51832470.009999998</v>
+      </c>
+      <c r="H2051">
+        <v>51832470.009999998</v>
+      </c>
+    </row>
+    <row r="2052" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2052" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2052" s="1">
+        <v>46083</v>
+      </c>
+      <c r="C2052" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2052">
+        <v>0</v>
+      </c>
+      <c r="E2052">
+        <v>0</v>
+      </c>
+      <c r="F2052">
+        <v>0</v>
+      </c>
+      <c r="G2052">
+        <v>375521.94</v>
+      </c>
+      <c r="H2052">
+        <v>375521.94</v>
+      </c>
+    </row>
+    <row r="2053" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2053" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2053" s="1">
+        <v>46083</v>
+      </c>
+      <c r="C2053" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2053">
+        <v>0</v>
+      </c>
+      <c r="E2053">
+        <v>0</v>
+      </c>
+      <c r="F2053">
+        <v>0</v>
+      </c>
+      <c r="G2053">
+        <v>967130.09</v>
+      </c>
+      <c r="H2053">
+        <v>967130.09</v>
+      </c>
+    </row>
+    <row r="2054" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2054" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B2054" s="1">
+        <v>46083</v>
+      </c>
+      <c r="C2054" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2054">
+        <v>5014.41</v>
+      </c>
+      <c r="E2054">
+        <v>291665.73</v>
+      </c>
+      <c r="F2054">
+        <v>-286651.32</v>
+      </c>
+      <c r="G2054">
+        <v>341133.24</v>
+      </c>
+      <c r="H2054">
+        <v>54481.919999999984</v>
+      </c>
+    </row>
+    <row r="2055" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2055" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B2055" s="1">
+        <v>46083</v>
+      </c>
+      <c r="C2055" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2055">
+        <v>0</v>
+      </c>
+      <c r="E2055">
+        <v>0</v>
+      </c>
+      <c r="F2055">
+        <v>0</v>
+      </c>
+      <c r="G2055">
+        <v>3387684.25</v>
+      </c>
+      <c r="H2055">
+        <v>3387684.25</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:L1691" xr:uid="{31E222C4-9EE5-4085-8D2B-84513C2B1175}"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>

--- a/data/1Saldos - ecossistema.xlsx
+++ b/data/1Saldos - ecossistema.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ALURA\Documents\Report de Saldos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F2FFAFC-2E6B-460F-88FC-3E2218DAB8E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70F639DC-8AA6-4FF4-A4BA-C0295B953302}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7EA03BAB-5D16-49FA-97CC-A81D8C595687}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4116" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4142" uniqueCount="17">
   <si>
     <t>Empresa</t>
   </si>
@@ -958,7 +958,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31E222C4-9EE5-4085-8D2B-84513C2B1175}">
-  <dimension ref="A1:L2055"/>
+  <dimension ref="A1:L2068"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.5546875" bestFit="1" customWidth="1"/>
@@ -54402,6 +54402,344 @@
         <v>3387684.25</v>
       </c>
     </row>
+    <row r="2056" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2056" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2056" s="1">
+        <v>46084</v>
+      </c>
+      <c r="C2056" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2056">
+        <v>0</v>
+      </c>
+      <c r="E2056">
+        <v>0</v>
+      </c>
+      <c r="F2056">
+        <v>0</v>
+      </c>
+      <c r="G2056">
+        <v>998204.61</v>
+      </c>
+      <c r="H2056">
+        <v>998204.61</v>
+      </c>
+    </row>
+    <row r="2057" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2057" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2057" s="1">
+        <v>46084</v>
+      </c>
+      <c r="C2057" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2057">
+        <v>3900.88</v>
+      </c>
+      <c r="E2057">
+        <v>0</v>
+      </c>
+      <c r="F2057">
+        <v>3900.88</v>
+      </c>
+      <c r="G2057">
+        <v>5450268.6699999999</v>
+      </c>
+      <c r="H2057">
+        <v>5454169.5499999998</v>
+      </c>
+    </row>
+    <row r="2058" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2058" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2058" s="1">
+        <v>46084</v>
+      </c>
+      <c r="C2058" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2058">
+        <v>755756.83</v>
+      </c>
+      <c r="E2058">
+        <v>0</v>
+      </c>
+      <c r="F2058">
+        <v>755756.83</v>
+      </c>
+      <c r="G2058">
+        <v>0</v>
+      </c>
+      <c r="H2058">
+        <v>755756.83</v>
+      </c>
+    </row>
+    <row r="2059" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2059" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2059" s="1">
+        <v>46084</v>
+      </c>
+      <c r="C2059" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2059">
+        <v>0</v>
+      </c>
+      <c r="E2059">
+        <v>0</v>
+      </c>
+      <c r="F2059">
+        <v>0</v>
+      </c>
+      <c r="G2059">
+        <v>14634941.17</v>
+      </c>
+      <c r="H2059">
+        <v>14634941.17</v>
+      </c>
+    </row>
+    <row r="2060" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2060" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2060" s="1">
+        <v>46084</v>
+      </c>
+      <c r="C2060" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2060">
+        <v>0</v>
+      </c>
+      <c r="E2060">
+        <v>0</v>
+      </c>
+      <c r="F2060">
+        <v>0</v>
+      </c>
+      <c r="G2060">
+        <v>490365.73</v>
+      </c>
+      <c r="H2060">
+        <v>490365.73</v>
+      </c>
+    </row>
+    <row r="2061" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2061" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2061" s="1">
+        <v>46084</v>
+      </c>
+      <c r="C2061" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2061">
+        <v>0</v>
+      </c>
+      <c r="E2061">
+        <v>0</v>
+      </c>
+      <c r="F2061">
+        <v>0</v>
+      </c>
+      <c r="G2061">
+        <v>2805161.33</v>
+      </c>
+      <c r="H2061">
+        <v>2805161.33</v>
+      </c>
+    </row>
+    <row r="2062" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2062" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2062" s="1">
+        <v>46084</v>
+      </c>
+      <c r="C2062" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2062">
+        <v>221170.91</v>
+      </c>
+      <c r="E2062">
+        <v>0</v>
+      </c>
+      <c r="F2062">
+        <v>221170.91</v>
+      </c>
+      <c r="G2062">
+        <v>8770566.0700000003</v>
+      </c>
+      <c r="H2062">
+        <v>8991736.9800000004</v>
+      </c>
+    </row>
+    <row r="2063" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2063" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2063" s="1">
+        <v>46084</v>
+      </c>
+      <c r="C2063" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2063">
+        <v>0</v>
+      </c>
+      <c r="E2063">
+        <v>6300</v>
+      </c>
+      <c r="F2063">
+        <v>-6300</v>
+      </c>
+      <c r="G2063">
+        <v>121825.76</v>
+      </c>
+      <c r="H2063">
+        <v>115525.75999999999</v>
+      </c>
+    </row>
+    <row r="2064" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2064" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2064" s="1">
+        <v>46084</v>
+      </c>
+      <c r="C2064" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2064">
+        <v>0</v>
+      </c>
+      <c r="E2064">
+        <v>0</v>
+      </c>
+      <c r="F2064">
+        <v>0</v>
+      </c>
+      <c r="G2064">
+        <v>51832470.009999998</v>
+      </c>
+      <c r="H2064">
+        <v>51832470.009999998</v>
+      </c>
+    </row>
+    <row r="2065" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2065" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2065" s="1">
+        <v>46084</v>
+      </c>
+      <c r="C2065" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2065">
+        <v>0</v>
+      </c>
+      <c r="E2065">
+        <v>0</v>
+      </c>
+      <c r="F2065">
+        <v>0</v>
+      </c>
+      <c r="G2065">
+        <v>375521.94</v>
+      </c>
+      <c r="H2065">
+        <v>375521.94</v>
+      </c>
+    </row>
+    <row r="2066" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2066" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2066" s="1">
+        <v>46084</v>
+      </c>
+      <c r="C2066" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2066">
+        <v>0</v>
+      </c>
+      <c r="E2066">
+        <v>0</v>
+      </c>
+      <c r="F2066">
+        <v>0</v>
+      </c>
+      <c r="G2066">
+        <v>967130.09</v>
+      </c>
+      <c r="H2066">
+        <v>967130.09</v>
+      </c>
+    </row>
+    <row r="2067" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2067" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B2067" s="1">
+        <v>46084</v>
+      </c>
+      <c r="C2067" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2067">
+        <v>4002.66</v>
+      </c>
+      <c r="E2067">
+        <v>0</v>
+      </c>
+      <c r="F2067">
+        <v>4002.66</v>
+      </c>
+      <c r="G2067">
+        <v>232886.46</v>
+      </c>
+      <c r="H2067">
+        <v>236889.12</v>
+      </c>
+    </row>
+    <row r="2068" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2068" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B2068" s="1">
+        <v>46084</v>
+      </c>
+      <c r="C2068" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2068">
+        <v>0</v>
+      </c>
+      <c r="E2068">
+        <v>0</v>
+      </c>
+      <c r="F2068">
+        <v>0</v>
+      </c>
+      <c r="G2068">
+        <v>3387684.25</v>
+      </c>
+      <c r="H2068">
+        <v>3387684.25</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:L1691" xr:uid="{31E222C4-9EE5-4085-8D2B-84513C2B1175}"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>

--- a/data/1Saldos - ecossistema.xlsx
+++ b/data/1Saldos - ecossistema.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ALURA\Documents\Report de Saldos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70F639DC-8AA6-4FF4-A4BA-C0295B953302}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B31D35E-467D-471A-893B-8EB20107C745}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7EA03BAB-5D16-49FA-97CC-A81D8C595687}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4142" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4168" uniqueCount="17">
   <si>
     <t>Empresa</t>
   </si>
@@ -958,7 +958,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31E222C4-9EE5-4085-8D2B-84513C2B1175}">
-  <dimension ref="A1:L2068"/>
+  <dimension ref="A1:L2081"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.5546875" bestFit="1" customWidth="1"/>
@@ -54740,6 +54740,344 @@
         <v>3387684.25</v>
       </c>
     </row>
+    <row r="2069" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2069" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2069" s="1">
+        <v>46085</v>
+      </c>
+      <c r="C2069" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2069">
+        <v>0</v>
+      </c>
+      <c r="E2069">
+        <v>0</v>
+      </c>
+      <c r="F2069">
+        <v>0</v>
+      </c>
+      <c r="G2069">
+        <v>998204.61</v>
+      </c>
+      <c r="H2069">
+        <v>998204.61</v>
+      </c>
+    </row>
+    <row r="2070" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2070" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2070" s="1">
+        <v>46085</v>
+      </c>
+      <c r="C2070" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2070">
+        <v>539595.69999999995</v>
+      </c>
+      <c r="E2070">
+        <v>0</v>
+      </c>
+      <c r="F2070">
+        <v>539595.69999999995</v>
+      </c>
+      <c r="G2070">
+        <v>0</v>
+      </c>
+      <c r="H2070">
+        <v>539595.69999999995</v>
+      </c>
+    </row>
+    <row r="2071" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2071" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2071" s="1">
+        <v>46085</v>
+      </c>
+      <c r="C2071" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2071">
+        <v>402899.37</v>
+      </c>
+      <c r="E2071">
+        <v>0</v>
+      </c>
+      <c r="F2071">
+        <v>402899.37</v>
+      </c>
+      <c r="G2071">
+        <v>0</v>
+      </c>
+      <c r="H2071">
+        <v>402899.37</v>
+      </c>
+    </row>
+    <row r="2072" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2072" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2072" s="1">
+        <v>46085</v>
+      </c>
+      <c r="C2072" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2072">
+        <v>0</v>
+      </c>
+      <c r="E2072">
+        <v>0</v>
+      </c>
+      <c r="F2072">
+        <v>0</v>
+      </c>
+      <c r="G2072">
+        <v>21872212.25</v>
+      </c>
+      <c r="H2072">
+        <v>21872212.25</v>
+      </c>
+    </row>
+    <row r="2073" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2073" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2073" s="1">
+        <v>46085</v>
+      </c>
+      <c r="C2073" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2073">
+        <v>0</v>
+      </c>
+      <c r="E2073">
+        <v>0</v>
+      </c>
+      <c r="F2073">
+        <v>0</v>
+      </c>
+      <c r="G2073">
+        <v>956122.66</v>
+      </c>
+      <c r="H2073">
+        <v>956122.66</v>
+      </c>
+    </row>
+    <row r="2074" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2074" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2074" s="1">
+        <v>46085</v>
+      </c>
+      <c r="C2074" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2074">
+        <v>0</v>
+      </c>
+      <c r="E2074">
+        <v>0</v>
+      </c>
+      <c r="F2074">
+        <v>0</v>
+      </c>
+      <c r="G2074">
+        <v>2805161.33</v>
+      </c>
+      <c r="H2074">
+        <v>2805161.33</v>
+      </c>
+    </row>
+    <row r="2075" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2075" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2075" s="1">
+        <v>46085</v>
+      </c>
+      <c r="C2075" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2075">
+        <v>944123.43</v>
+      </c>
+      <c r="E2075">
+        <v>0</v>
+      </c>
+      <c r="F2075">
+        <v>944123.43</v>
+      </c>
+      <c r="G2075">
+        <v>0</v>
+      </c>
+      <c r="H2075">
+        <v>944123.43</v>
+      </c>
+    </row>
+    <row r="2076" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2076" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2076" s="1">
+        <v>46085</v>
+      </c>
+      <c r="C2076" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2076">
+        <v>0</v>
+      </c>
+      <c r="E2076">
+        <v>0</v>
+      </c>
+      <c r="F2076">
+        <v>0</v>
+      </c>
+      <c r="G2076">
+        <v>115444.62</v>
+      </c>
+      <c r="H2076">
+        <v>115444.62</v>
+      </c>
+    </row>
+    <row r="2077" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2077" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2077" s="1">
+        <v>46085</v>
+      </c>
+      <c r="C2077" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2077">
+        <v>0</v>
+      </c>
+      <c r="E2077">
+        <v>0</v>
+      </c>
+      <c r="F2077">
+        <v>0</v>
+      </c>
+      <c r="G2077">
+        <v>63715186.509999998</v>
+      </c>
+      <c r="H2077">
+        <v>63715186.509999998</v>
+      </c>
+    </row>
+    <row r="2078" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2078" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2078" s="1">
+        <v>46085</v>
+      </c>
+      <c r="C2078" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2078">
+        <v>0</v>
+      </c>
+      <c r="E2078">
+        <v>0</v>
+      </c>
+      <c r="F2078">
+        <v>0</v>
+      </c>
+      <c r="G2078">
+        <v>375521.94</v>
+      </c>
+      <c r="H2078">
+        <v>375521.94</v>
+      </c>
+    </row>
+    <row r="2079" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2079" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2079" s="1">
+        <v>46085</v>
+      </c>
+      <c r="C2079" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2079">
+        <v>0</v>
+      </c>
+      <c r="E2079">
+        <v>0</v>
+      </c>
+      <c r="F2079">
+        <v>0</v>
+      </c>
+      <c r="G2079">
+        <v>967330.44</v>
+      </c>
+      <c r="H2079">
+        <v>967330.44</v>
+      </c>
+    </row>
+    <row r="2080" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2080" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B2080" s="1">
+        <v>46085</v>
+      </c>
+      <c r="C2080" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2080">
+        <v>101624.24</v>
+      </c>
+      <c r="E2080">
+        <v>0</v>
+      </c>
+      <c r="F2080">
+        <v>101624.24</v>
+      </c>
+      <c r="G2080">
+        <v>0</v>
+      </c>
+      <c r="H2080">
+        <v>101624.24</v>
+      </c>
+    </row>
+    <row r="2081" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2081" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B2081" s="1">
+        <v>46085</v>
+      </c>
+      <c r="C2081" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2081">
+        <v>0</v>
+      </c>
+      <c r="E2081">
+        <v>0</v>
+      </c>
+      <c r="F2081">
+        <v>0</v>
+      </c>
+      <c r="G2081">
+        <v>3390020.45</v>
+      </c>
+      <c r="H2081">
+        <v>3390020.45</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:L1691" xr:uid="{31E222C4-9EE5-4085-8D2B-84513C2B1175}"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>

--- a/data/1Saldos - ecossistema.xlsx
+++ b/data/1Saldos - ecossistema.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ALURA\Documents\Report de Saldos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B31D35E-467D-471A-893B-8EB20107C745}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0DAAE05-6E16-4CD0-A447-256B46A157D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7EA03BAB-5D16-49FA-97CC-A81D8C595687}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4168" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4194" uniqueCount="17">
   <si>
     <t>Empresa</t>
   </si>
@@ -958,7 +958,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31E222C4-9EE5-4085-8D2B-84513C2B1175}">
-  <dimension ref="A1:L2081"/>
+  <dimension ref="A1:L2094"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.5546875" bestFit="1" customWidth="1"/>
@@ -55078,6 +55078,344 @@
         <v>3390020.45</v>
       </c>
     </row>
+    <row r="2082" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2082" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2082" s="1">
+        <v>46086</v>
+      </c>
+      <c r="C2082" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2082">
+        <v>0</v>
+      </c>
+      <c r="E2082">
+        <v>0</v>
+      </c>
+      <c r="F2082">
+        <v>0</v>
+      </c>
+      <c r="G2082">
+        <v>998204.61</v>
+      </c>
+      <c r="H2082">
+        <v>998204.61</v>
+      </c>
+    </row>
+    <row r="2083" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2083" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2083" s="1">
+        <v>46086</v>
+      </c>
+      <c r="C2083" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2083">
+        <v>619806.16</v>
+      </c>
+      <c r="E2083">
+        <v>1769094.96</v>
+      </c>
+      <c r="F2083">
+        <v>-1149288.7999999998</v>
+      </c>
+      <c r="G2083">
+        <v>0</v>
+      </c>
+      <c r="H2083">
+        <v>-1149288.7999999998</v>
+      </c>
+    </row>
+    <row r="2084" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2084" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2084" s="1">
+        <v>46086</v>
+      </c>
+      <c r="C2084" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2084">
+        <v>437733.97</v>
+      </c>
+      <c r="E2084">
+        <v>0</v>
+      </c>
+      <c r="F2084">
+        <v>437733.97</v>
+      </c>
+      <c r="G2084">
+        <v>0</v>
+      </c>
+      <c r="H2084">
+        <v>437733.97</v>
+      </c>
+    </row>
+    <row r="2085" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2085" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2085" s="1">
+        <v>46086</v>
+      </c>
+      <c r="C2085" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2085">
+        <v>0</v>
+      </c>
+      <c r="E2085">
+        <v>0</v>
+      </c>
+      <c r="F2085">
+        <v>0</v>
+      </c>
+      <c r="G2085">
+        <v>21960688.420000002</v>
+      </c>
+      <c r="H2085">
+        <v>21960688.420000002</v>
+      </c>
+    </row>
+    <row r="2086" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2086" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2086" s="1">
+        <v>46086</v>
+      </c>
+      <c r="C2086" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2086">
+        <v>0</v>
+      </c>
+      <c r="E2086">
+        <v>0</v>
+      </c>
+      <c r="F2086">
+        <v>0</v>
+      </c>
+      <c r="G2086">
+        <v>22081.62</v>
+      </c>
+      <c r="H2086">
+        <v>22081.62</v>
+      </c>
+    </row>
+    <row r="2087" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2087" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2087" s="1">
+        <v>46086</v>
+      </c>
+      <c r="C2087" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2087">
+        <v>0</v>
+      </c>
+      <c r="E2087">
+        <v>0</v>
+      </c>
+      <c r="F2087">
+        <v>0</v>
+      </c>
+      <c r="G2087">
+        <v>2805161.33</v>
+      </c>
+      <c r="H2087">
+        <v>2805161.33</v>
+      </c>
+    </row>
+    <row r="2088" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2088" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2088" s="1">
+        <v>46086</v>
+      </c>
+      <c r="C2088" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2088">
+        <v>3391528.86</v>
+      </c>
+      <c r="E2088">
+        <v>4750878.54</v>
+      </c>
+      <c r="F2088">
+        <v>-1359349.6800000002</v>
+      </c>
+      <c r="G2088">
+        <v>0</v>
+      </c>
+      <c r="H2088">
+        <v>-1359349.6800000002</v>
+      </c>
+    </row>
+    <row r="2089" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2089" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2089" s="1">
+        <v>46086</v>
+      </c>
+      <c r="C2089" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2089">
+        <v>0</v>
+      </c>
+      <c r="E2089">
+        <v>0</v>
+      </c>
+      <c r="F2089">
+        <v>0</v>
+      </c>
+      <c r="G2089">
+        <v>115444.62</v>
+      </c>
+      <c r="H2089">
+        <v>115444.62</v>
+      </c>
+    </row>
+    <row r="2090" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2090" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2090" s="1">
+        <v>46086</v>
+      </c>
+      <c r="C2090" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2090">
+        <v>0</v>
+      </c>
+      <c r="E2090">
+        <v>0</v>
+      </c>
+      <c r="F2090">
+        <v>0</v>
+      </c>
+      <c r="G2090">
+        <v>62693267.270000003</v>
+      </c>
+      <c r="H2090">
+        <v>62693267.270000003</v>
+      </c>
+    </row>
+    <row r="2091" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2091" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2091" s="1">
+        <v>46086</v>
+      </c>
+      <c r="C2091" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2091">
+        <v>0</v>
+      </c>
+      <c r="E2091">
+        <v>0</v>
+      </c>
+      <c r="F2091">
+        <v>0</v>
+      </c>
+      <c r="G2091">
+        <v>375521.94</v>
+      </c>
+      <c r="H2091">
+        <v>375521.94</v>
+      </c>
+    </row>
+    <row r="2092" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2092" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2092" s="1">
+        <v>46086</v>
+      </c>
+      <c r="C2092" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2092">
+        <v>0</v>
+      </c>
+      <c r="E2092">
+        <v>0</v>
+      </c>
+      <c r="F2092">
+        <v>0</v>
+      </c>
+      <c r="G2092">
+        <v>968790.12</v>
+      </c>
+      <c r="H2092">
+        <v>968790.12</v>
+      </c>
+    </row>
+    <row r="2093" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2093" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B2093" s="1">
+        <v>46086</v>
+      </c>
+      <c r="C2093" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2093">
+        <v>139701.9</v>
+      </c>
+      <c r="E2093">
+        <v>67199.649999999994</v>
+      </c>
+      <c r="F2093">
+        <v>72502.25</v>
+      </c>
+      <c r="G2093">
+        <v>0</v>
+      </c>
+      <c r="H2093">
+        <v>72502.25</v>
+      </c>
+    </row>
+    <row r="2094" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2094" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B2094" s="1">
+        <v>46086</v>
+      </c>
+      <c r="C2094" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2094">
+        <v>0</v>
+      </c>
+      <c r="E2094">
+        <v>0</v>
+      </c>
+      <c r="F2094">
+        <v>0</v>
+      </c>
+      <c r="G2094">
+        <v>3593577.87</v>
+      </c>
+      <c r="H2094">
+        <v>3593577.87</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:L1691" xr:uid="{31E222C4-9EE5-4085-8D2B-84513C2B1175}"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>

--- a/data/1Saldos - ecossistema.xlsx
+++ b/data/1Saldos - ecossistema.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ALURA\Documents\Report de Saldos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0DAAE05-6E16-4CD0-A447-256B46A157D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FE8965E-9689-40FA-B59C-06E4E26660C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7EA03BAB-5D16-49FA-97CC-A81D8C595687}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4194" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4220" uniqueCount="17">
   <si>
     <t>Empresa</t>
   </si>
@@ -958,7 +958,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31E222C4-9EE5-4085-8D2B-84513C2B1175}">
-  <dimension ref="A1:L2094"/>
+  <dimension ref="A1:L2107"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.5546875" bestFit="1" customWidth="1"/>
@@ -55416,6 +55416,344 @@
         <v>3593577.87</v>
       </c>
     </row>
+    <row r="2095" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2095" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2095" s="1">
+        <v>46090</v>
+      </c>
+      <c r="C2095" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2095">
+        <v>0</v>
+      </c>
+      <c r="E2095">
+        <v>0</v>
+      </c>
+      <c r="F2095">
+        <v>0</v>
+      </c>
+      <c r="G2095">
+        <v>998204.61</v>
+      </c>
+      <c r="H2095">
+        <v>998204.61</v>
+      </c>
+    </row>
+    <row r="2096" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2096" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2096" s="1">
+        <v>46090</v>
+      </c>
+      <c r="C2096" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2096">
+        <v>11530.21</v>
+      </c>
+      <c r="E2096">
+        <v>4503.16</v>
+      </c>
+      <c r="F2096">
+        <v>7027.0499999999993</v>
+      </c>
+      <c r="G2096">
+        <v>49989.51</v>
+      </c>
+      <c r="H2096">
+        <v>57016.56</v>
+      </c>
+    </row>
+    <row r="2097" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2097" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2097" s="1">
+        <v>46090</v>
+      </c>
+      <c r="C2097" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2097">
+        <v>105815.08</v>
+      </c>
+      <c r="E2097">
+        <v>0</v>
+      </c>
+      <c r="F2097">
+        <v>105815.08</v>
+      </c>
+      <c r="G2097">
+        <v>0</v>
+      </c>
+      <c r="H2097">
+        <v>105815.08</v>
+      </c>
+    </row>
+    <row r="2098" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2098" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2098" s="1">
+        <v>46090</v>
+      </c>
+      <c r="C2098" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2098">
+        <v>0</v>
+      </c>
+      <c r="E2098">
+        <v>0</v>
+      </c>
+      <c r="F2098">
+        <v>0</v>
+      </c>
+      <c r="G2098">
+        <v>22771686.100000001</v>
+      </c>
+      <c r="H2098">
+        <v>22771686.100000001</v>
+      </c>
+    </row>
+    <row r="2099" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2099" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2099" s="1">
+        <v>46090</v>
+      </c>
+      <c r="C2099" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2099">
+        <v>0</v>
+      </c>
+      <c r="E2099">
+        <v>0</v>
+      </c>
+      <c r="F2099">
+        <v>0</v>
+      </c>
+      <c r="G2099">
+        <v>87568.97</v>
+      </c>
+      <c r="H2099">
+        <v>87568.97</v>
+      </c>
+    </row>
+    <row r="2100" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2100" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2100" s="1">
+        <v>46090</v>
+      </c>
+      <c r="C2100" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2100">
+        <v>0</v>
+      </c>
+      <c r="E2100">
+        <v>0</v>
+      </c>
+      <c r="F2100">
+        <v>0</v>
+      </c>
+      <c r="G2100">
+        <v>2805161.33</v>
+      </c>
+      <c r="H2100">
+        <v>2805161.33</v>
+      </c>
+    </row>
+    <row r="2101" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2101" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2101" s="1">
+        <v>46090</v>
+      </c>
+      <c r="C2101" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2101">
+        <v>188844.64</v>
+      </c>
+      <c r="E2101">
+        <v>0</v>
+      </c>
+      <c r="F2101">
+        <v>188844.64</v>
+      </c>
+      <c r="G2101">
+        <v>499954.92</v>
+      </c>
+      <c r="H2101">
+        <v>688799.56</v>
+      </c>
+    </row>
+    <row r="2102" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2102" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2102" s="1">
+        <v>46090</v>
+      </c>
+      <c r="C2102" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2102">
+        <v>0</v>
+      </c>
+      <c r="E2102">
+        <v>0</v>
+      </c>
+      <c r="F2102">
+        <v>0</v>
+      </c>
+      <c r="G2102">
+        <v>107090.44</v>
+      </c>
+      <c r="H2102">
+        <v>107090.44</v>
+      </c>
+    </row>
+    <row r="2103" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2103" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2103" s="1">
+        <v>46090</v>
+      </c>
+      <c r="C2103" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2103">
+        <v>0</v>
+      </c>
+      <c r="E2103">
+        <v>0</v>
+      </c>
+      <c r="F2103">
+        <v>0</v>
+      </c>
+      <c r="G2103">
+        <v>70778383.469999999</v>
+      </c>
+      <c r="H2103">
+        <v>70778383.469999999</v>
+      </c>
+    </row>
+    <row r="2104" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2104" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2104" s="1">
+        <v>46090</v>
+      </c>
+      <c r="C2104" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2104">
+        <v>0</v>
+      </c>
+      <c r="E2104">
+        <v>0</v>
+      </c>
+      <c r="F2104">
+        <v>0</v>
+      </c>
+      <c r="G2104">
+        <v>375521.94</v>
+      </c>
+      <c r="H2104">
+        <v>375521.94</v>
+      </c>
+    </row>
+    <row r="2105" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2105" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2105" s="1">
+        <v>46090</v>
+      </c>
+      <c r="C2105" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2105">
+        <v>0</v>
+      </c>
+      <c r="E2105">
+        <v>0</v>
+      </c>
+      <c r="F2105">
+        <v>0</v>
+      </c>
+      <c r="G2105">
+        <v>969725.66</v>
+      </c>
+      <c r="H2105">
+        <v>969725.66</v>
+      </c>
+    </row>
+    <row r="2106" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2106" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B2106" s="1">
+        <v>46090</v>
+      </c>
+      <c r="C2106" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2106">
+        <v>2945.89</v>
+      </c>
+      <c r="E2106">
+        <v>0</v>
+      </c>
+      <c r="F2106">
+        <v>2945.89</v>
+      </c>
+      <c r="G2106">
+        <v>17999.07</v>
+      </c>
+      <c r="H2106">
+        <v>20944.96</v>
+      </c>
+    </row>
+    <row r="2107" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2107" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B2107" s="1">
+        <v>46090</v>
+      </c>
+      <c r="C2107" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2107">
+        <v>0</v>
+      </c>
+      <c r="E2107">
+        <v>0</v>
+      </c>
+      <c r="F2107">
+        <v>0</v>
+      </c>
+      <c r="G2107">
+        <v>3699028.48</v>
+      </c>
+      <c r="H2107">
+        <v>3699028.48</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:L1691" xr:uid="{31E222C4-9EE5-4085-8D2B-84513C2B1175}"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>

--- a/data/1Saldos - ecossistema.xlsx
+++ b/data/1Saldos - ecossistema.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ALURA\Documents\Report de Saldos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FE8965E-9689-40FA-B59C-06E4E26660C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8E9D12E-556B-4F20-830E-8E5075468ACC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7EA03BAB-5D16-49FA-97CC-A81D8C595687}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7EA03BAB-5D16-49FA-97CC-A81D8C595687}"/>
   </bookViews>
   <sheets>
     <sheet name="in" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4220" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4246" uniqueCount="17">
   <si>
     <t>Empresa</t>
   </si>
@@ -958,7 +958,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31E222C4-9EE5-4085-8D2B-84513C2B1175}">
-  <dimension ref="A1:L2107"/>
+  <dimension ref="A1:L2120"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.5546875" bestFit="1" customWidth="1"/>
@@ -55754,6 +55754,344 @@
         <v>3699028.48</v>
       </c>
     </row>
+    <row r="2108" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2108" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2108" s="1">
+        <v>46091</v>
+      </c>
+      <c r="C2108" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2108">
+        <v>0</v>
+      </c>
+      <c r="E2108">
+        <v>0</v>
+      </c>
+      <c r="F2108">
+        <v>0</v>
+      </c>
+      <c r="G2108">
+        <v>998204.61</v>
+      </c>
+      <c r="H2108">
+        <v>998204.61</v>
+      </c>
+    </row>
+    <row r="2109" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2109" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2109" s="1">
+        <v>46091</v>
+      </c>
+      <c r="C2109" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2109">
+        <v>19647.71</v>
+      </c>
+      <c r="E2109">
+        <v>1223812.1400000001</v>
+      </c>
+      <c r="F2109">
+        <v>-1204164.4300000002</v>
+      </c>
+      <c r="G2109">
+        <v>0</v>
+      </c>
+      <c r="H2109">
+        <v>-1204164.4300000002</v>
+      </c>
+    </row>
+    <row r="2110" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2110" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2110" s="1">
+        <v>46091</v>
+      </c>
+      <c r="C2110" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2110">
+        <v>188349.7</v>
+      </c>
+      <c r="E2110">
+        <v>0</v>
+      </c>
+      <c r="F2110">
+        <v>188349.7</v>
+      </c>
+      <c r="G2110">
+        <v>0</v>
+      </c>
+      <c r="H2110">
+        <v>188349.7</v>
+      </c>
+    </row>
+    <row r="2111" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2111" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2111" s="1">
+        <v>46091</v>
+      </c>
+      <c r="C2111" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2111">
+        <v>0</v>
+      </c>
+      <c r="E2111">
+        <v>0</v>
+      </c>
+      <c r="F2111">
+        <v>0</v>
+      </c>
+      <c r="G2111">
+        <v>22784069.719999999</v>
+      </c>
+      <c r="H2111">
+        <v>22784069.719999999</v>
+      </c>
+    </row>
+    <row r="2112" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2112" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2112" s="1">
+        <v>46091</v>
+      </c>
+      <c r="C2112" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2112">
+        <v>0</v>
+      </c>
+      <c r="E2112">
+        <v>0</v>
+      </c>
+      <c r="F2112">
+        <v>0</v>
+      </c>
+      <c r="G2112">
+        <v>293553.59000000003</v>
+      </c>
+      <c r="H2112">
+        <v>293553.59000000003</v>
+      </c>
+    </row>
+    <row r="2113" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2113" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2113" s="1">
+        <v>46091</v>
+      </c>
+      <c r="C2113" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2113">
+        <v>0</v>
+      </c>
+      <c r="E2113">
+        <v>0</v>
+      </c>
+      <c r="F2113">
+        <v>0</v>
+      </c>
+      <c r="G2113">
+        <v>2805161.33</v>
+      </c>
+      <c r="H2113">
+        <v>2805161.33</v>
+      </c>
+    </row>
+    <row r="2114" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2114" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2114" s="1">
+        <v>46091</v>
+      </c>
+      <c r="C2114" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2114">
+        <v>175630.46</v>
+      </c>
+      <c r="E2114">
+        <v>3626340.15</v>
+      </c>
+      <c r="F2114">
+        <v>-3450709.69</v>
+      </c>
+      <c r="G2114">
+        <v>0</v>
+      </c>
+      <c r="H2114">
+        <v>-3450709.69</v>
+      </c>
+    </row>
+    <row r="2115" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2115" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2115" s="1">
+        <v>46091</v>
+      </c>
+      <c r="C2115" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2115">
+        <v>0</v>
+      </c>
+      <c r="E2115">
+        <v>6644.45</v>
+      </c>
+      <c r="F2115">
+        <v>-6644.45</v>
+      </c>
+      <c r="G2115">
+        <v>107090.44</v>
+      </c>
+      <c r="H2115">
+        <v>100445.99</v>
+      </c>
+    </row>
+    <row r="2116" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2116" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2116" s="1">
+        <v>46091</v>
+      </c>
+      <c r="C2116" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2116">
+        <v>0</v>
+      </c>
+      <c r="E2116">
+        <v>0</v>
+      </c>
+      <c r="F2116">
+        <v>0</v>
+      </c>
+      <c r="G2116">
+        <v>70817012.75</v>
+      </c>
+      <c r="H2116">
+        <v>70817012.75</v>
+      </c>
+    </row>
+    <row r="2117" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2117" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2117" s="1">
+        <v>46091</v>
+      </c>
+      <c r="C2117" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2117">
+        <v>0</v>
+      </c>
+      <c r="E2117">
+        <v>0</v>
+      </c>
+      <c r="F2117">
+        <v>0</v>
+      </c>
+      <c r="G2117">
+        <v>375521.94</v>
+      </c>
+      <c r="H2117">
+        <v>375521.94</v>
+      </c>
+    </row>
+    <row r="2118" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2118" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2118" s="1">
+        <v>46091</v>
+      </c>
+      <c r="C2118" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2118">
+        <v>0</v>
+      </c>
+      <c r="E2118">
+        <v>0</v>
+      </c>
+      <c r="F2118">
+        <v>0</v>
+      </c>
+      <c r="G2118">
+        <v>969897.28</v>
+      </c>
+      <c r="H2118">
+        <v>969897.28</v>
+      </c>
+    </row>
+    <row r="2119" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2119" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B2119" s="1">
+        <v>46091</v>
+      </c>
+      <c r="C2119" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2119">
+        <v>4000.45</v>
+      </c>
+      <c r="E2119">
+        <v>214257.58</v>
+      </c>
+      <c r="F2119">
+        <v>-210257.12999999998</v>
+      </c>
+      <c r="G2119">
+        <v>0</v>
+      </c>
+      <c r="H2119">
+        <v>-210257.12999999998</v>
+      </c>
+    </row>
+    <row r="2120" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2120" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B2120" s="1">
+        <v>46091</v>
+      </c>
+      <c r="C2120" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2120">
+        <v>0</v>
+      </c>
+      <c r="E2120">
+        <v>0</v>
+      </c>
+      <c r="F2120">
+        <v>0</v>
+      </c>
+      <c r="G2120">
+        <v>3701872.56</v>
+      </c>
+      <c r="H2120">
+        <v>3701872.56</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:L1691" xr:uid="{31E222C4-9EE5-4085-8D2B-84513C2B1175}"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
